--- a/data/trans_dic/IP11C$ingresado-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,7</t>
+          <t>0,0; 32,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,58</t>
+          <t>0,0; 31,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,35</t>
+          <t>0,0; 24,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,68</t>
+          <t>0,0; 17,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,36</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,39</t>
+          <t>0,0; 15,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,94</t>
+          <t>0,0; 33,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,74</t>
+          <t>0,0; 62,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 21,61</t>
+          <t>2,41; 23,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,64</t>
+          <t>0,0; 27,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 16,71</t>
+          <t>1,52; 17,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,27</t>
+          <t>0,0; 19,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,3</t>
+          <t>0,0; 26,62</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,54</t>
+          <t>0,0; 24,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,4</t>
+          <t>0,0; 39,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,77</t>
+          <t>0,0; 67,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,53</t>
+          <t>0,0; 39,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,01</t>
+          <t>0,0; 33,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,38</t>
+          <t>0,0; 38,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,1</t>
+          <t>0,0; 23,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 24,84</t>
+          <t>2,61; 24,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,45</t>
+          <t>0,0; 27,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,89</t>
+          <t>0,0; 28,22</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,27</t>
+          <t>0,0; 34,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,94</t>
+          <t>0,0; 28,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,04</t>
+          <t>0,0; 28,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,37</t>
+          <t>0,0; 35,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,06</t>
+          <t>0,0; 25,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,33</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,78</t>
+          <t>0,0; 32,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,25</t>
+          <t>0,0; 18,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 16,3</t>
+          <t>1,72; 16,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,17</t>
+          <t>0,0; 14,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,34</t>
+          <t>0,0; 23,64</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,51</t>
+          <t>2,15; 12,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 20,42</t>
+          <t>2,0; 20,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 26,27</t>
+          <t>2,48; 29,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,22</t>
+          <t>1,78; 12,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,19</t>
+          <t>3,57; 14,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,42</t>
+          <t>0,0; 14,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,21</t>
+          <t>0,0; 14,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,48</t>
+          <t>1,33; 8,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,77; 11,87</t>
+          <t>3,88; 11,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 12,43</t>
+          <t>1,89; 12,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 15,48</t>
+          <t>2,72; 15,29</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3483</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2189</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1337</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2545</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3573</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2095</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2861</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2102</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2330</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>681; 6593</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3167</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>711; 8373</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3496</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2469</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2614</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2489</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4419</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4217</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4665</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4603</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>607; 5740</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5085</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3550</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1626</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3327</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3390</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2765</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2785</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3179</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5242</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3037</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4104</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>607; 5846</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3572</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4074</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1741</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8782</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4102</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6493</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>466; 4782</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>426; 5006</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>828; 5819</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2622; 10939</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6094</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3587</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1090; 6957</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4854; 14751</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1208; 7742</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1118; 6299</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$ingresado-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Edad-trans_dic.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,51</t>
+          <t>0,0; 33,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,11</t>
+          <t>0,0; 46,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,08</t>
+          <t>0,0; 19,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,93</t>
+          <t>0,0; 18,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 84,36</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,49</t>
+          <t>0,0; 19,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,12</t>
+          <t>0,0; 34,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,66</t>
+          <t>0,0; 59,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 23,35</t>
+          <t>2,42; 24,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,83</t>
+          <t>0,0; 23,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 17,93</t>
+          <t>2,68; 17,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,72</t>
+          <t>0,0; 20,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,62</t>
+          <t>0,0; 24,98</t>
         </is>
       </c>
     </row>
@@ -1002,32 +1002,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,25</t>
+          <t>0,0; 29,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>0,0; 42,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,51</t>
+          <t>0,0; 64,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,95</t>
+          <t>0,0; 34,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,85</t>
+          <t>0,0; 35,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,27</t>
+          <t>0,0; 32,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,18</t>
+          <t>0,0; 20,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 24,71</t>
+          <t>2,61; 24,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,55</t>
+          <t>0,0; 29,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,22</t>
+          <t>0,0; 25,03</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,59</t>
+          <t>0,0; 32,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,84</t>
+          <t>0,0; 29,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,69</t>
+          <t>0,0; 32,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,71</t>
+          <t>0,0; 48,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,7</t>
+          <t>0,0; 21,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>0,0; 21,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,18</t>
+          <t>0,0; 29,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,67</t>
+          <t>0,0; 22,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 16,6</t>
+          <t>1,79; 17,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,85</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,64</t>
+          <t>0,0; 19,68</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 11,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,56</t>
+          <t>2,13; 12,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 20,46</t>
+          <t>2,03; 19,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 29,19</t>
+          <t>2,32; 26,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,51</t>
+          <t>1,4; 12,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 14,91</t>
+          <t>3,58; 15,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,96</t>
+          <t>0,0; 14,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,93</t>
+          <t>0,0; 15,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,5</t>
+          <t>1,47; 8,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,79</t>
+          <t>3,98; 11,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,08</t>
+          <t>1,79; 12,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,29</t>
+          <t>2,8; 16,65</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3483</t>
+          <t>0; 3604</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2189</t>
+          <t>0; 3294</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2545</t>
+          <t>0; 2094</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3573</t>
+          <t>0; 3589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2095</t>
+          <t>0; 1767</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>0; 3517</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2102</t>
+          <t>0; 2160</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2330</t>
+          <t>0; 2219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>681; 6593</t>
+          <t>684; 6906</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3167</t>
+          <t>0; 2649</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>711; 8373</t>
+          <t>1252; 8000</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3496</t>
+          <t>0; 3664</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2469</t>
+          <t>0; 2317</t>
         </is>
       </c>
     </row>
@@ -2066,32 +2066,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2614</t>
+          <t>0; 3199</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2489</t>
+          <t>0; 2642</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3293</t>
+          <t>0; 3133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4419</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>0; 4434</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4665</t>
+          <t>0; 3977</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4603</t>
+          <t>0; 4077</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>607; 5740</t>
+          <t>607; 5634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5085</t>
+          <t>0; 5531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3550</t>
+          <t>0; 3149</t>
         </is>
       </c>
     </row>
@@ -2269,32 +2269,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3327</t>
+          <t>0; 3151</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3390</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2765</t>
+          <t>0; 3161</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2785</t>
+          <t>0; 3785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>0; 2667</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5242</t>
+          <t>0; 5076</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2304,27 +2304,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3037</t>
+          <t>0; 2764</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 4928</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>607; 5846</t>
+          <t>631; 6105</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3572</t>
+          <t>0; 2668</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4074</t>
+          <t>0; 3391</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4102</t>
+          <t>0; 3891</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1113; 6493</t>
+          <t>1104; 6523</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>466; 4782</t>
+          <t>475; 4666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>426; 5006</t>
+          <t>398; 4493</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>828; 5819</t>
+          <t>649; 6043</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2622; 10939</t>
+          <t>2626; 11425</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 5980</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3587</t>
+          <t>0; 3831</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1090; 6957</t>
+          <t>1203; 7132</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4854; 14751</t>
+          <t>4976; 14887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1208; 7742</t>
+          <t>1150; 8103</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1118; 6299</t>
+          <t>1151; 6858</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$ingresado-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52,56%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,34%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -717,14 +717,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 30,58</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 33,64</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -732,37 +732,37 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 46,81</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 33,7</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,82</t>
+          <t>0,0; 24,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,01</t>
+          <t>0,0; 17,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,36</t>
+          <t>0,0; 87,92</t>
         </is>
       </c>
     </row>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>3,8%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,55%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>7,09%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,04</t>
+          <t>2,4; 21,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,04</t>
+          <t>0,0; 29,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 24,46</t>
+          <t>0,0; 19,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,28</t>
+          <t>0,0; 33,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 51,03</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 17,13</t>
+          <t>2,64; 16,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,67</t>
+          <t>0,0; 20,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,98</t>
+          <t>0,0; 26,45</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,65%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,85%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 43,53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 32,01</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 38,38</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,68</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 42,17</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 64,22</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,59</t>
+          <t>0,0; 25,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,62</t>
+          <t>0,0; 50,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 58,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,54</t>
+          <t>0,0; 30,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 24,25</t>
+          <t>2,69; 24,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,97</t>
+          <t>0,0; 29,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,03</t>
+          <t>0,0; 32,39</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,69%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,76</t>
+          <t>0,0; 26,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,21</t>
+          <t>0,0; 21,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,54</t>
+          <t>0,0; 24,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,56</t>
+          <t>0,0; 38,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,62</t>
+          <t>0,0; 28,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,3</t>
+          <t>0,0; 35,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,41</t>
+          <t>0,0; 22,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 17,33</t>
+          <t>1,78; 16,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>0,0; 14,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,68</t>
+          <t>0,0; 21,45</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,98%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,45%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,02</t>
+          <t>1,29; 13,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,61</t>
+          <t>2,85; 15,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,97</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 26,2</t>
+          <t>0,0; 15,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,99</t>
+          <t>0,0; 12,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 15,57</t>
+          <t>1,29; 11,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,68</t>
+          <t>2,01; 20,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,94</t>
+          <t>2,09; 25,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,72</t>
+          <t>1,47; 8,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,9</t>
+          <t>3,77; 11,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 12,64</t>
+          <t>1,76; 12,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,65</t>
+          <t>2,2; 15,23</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,62 +1577,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>626</t>
         </is>
       </c>
     </row>
@@ -1645,14 +1645,14 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 2152</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3604</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1660,37 +1660,37 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 1191</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3294</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0; 3610</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1337</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2094</t>
+          <t>0; 2572</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3589</t>
+          <t>0; 3521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1767</t>
+          <t>0; 1545</t>
         </is>
       </c>
     </row>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1790,44 +1790,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>702</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>479</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>3312</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3517</t>
+          <t>677; 6103</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2160</t>
+          <t>0; 3372</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2219</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,37 +1878,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>684; 6906</t>
+          <t>0; 3581</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2649</t>
+          <t>0; 2154</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>0; 1852</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1252; 8000</t>
+          <t>1233; 7804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3664</t>
+          <t>0; 3592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2317</t>
+          <t>0; 2203</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1425</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2062</t>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>667</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 4814</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3988</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4679</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3199</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3133</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3809</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4434</t>
+          <t>0; 2752</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3977</t>
+          <t>0; 3158</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2865</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4077</t>
+          <t>0; 5977</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>607; 5634</t>
+          <t>625; 5772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5531</t>
+          <t>0; 5434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3149</t>
+          <t>0; 4031</t>
         </is>
       </c>
     </row>
@@ -2138,32 +2138,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2201,62 +2201,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1626</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1626</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1381</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1045</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3151</t>
+          <t>0; 3223</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3433</t>
+          <t>0; 5007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3161</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3785</t>
+          <t>0; 2171</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2667</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5076</t>
+          <t>0; 3402</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3281</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2764</t>
+          <t>0; 2865</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4928</t>
+          <t>0; 4892</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>631; 6105</t>
+          <t>628; 5743</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2668</t>
+          <t>0; 3408</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3391</t>
+          <t>0; 3625</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3093</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1740</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2557</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2705</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3891</t>
+          <t>599; 6149</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1104; 6523</t>
+          <t>2089; 11146</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475; 4666</t>
+          <t>0; 5466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>398; 4493</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>649; 6043</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2626; 11425</t>
+          <t>669; 5952</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5980</t>
+          <t>471; 4772</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3831</t>
+          <t>359; 4385</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1203; 7132</t>
+          <t>1204; 6940</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4976; 14887</t>
+          <t>4717; 14850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1150; 8103</t>
+          <t>1126; 7966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1151; 6858</t>
+          <t>869; 6005</t>
         </is>
       </c>
     </row>
